--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488049_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488049_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1511</v>
+        <v>4.3985</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9033</v>
+        <v>1.1507</v>
       </c>
       <c r="F2" t="n">
         <v>3.2478</v>
@@ -610,10 +610,10 @@
         <v>2.9733</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0645</v>
+        <v>0.312</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1638</v>
+        <v>0.4113</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0993</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2954</v>
+        <v>3.4358</v>
       </c>
       <c r="E3" t="n">
         <v>3.1298</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1656</v>
+        <v>0.306</v>
       </c>
       <c r="G3" t="n">
         <v>3.2642</v>
@@ -688,13 +688,13 @@
         <v>0.1982</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.167</v>
+        <v>-0.0266</v>
       </c>
       <c r="T3" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0422</v>
+        <v>0.0982</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4159</v>
+        <v>3.0438</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0762</v>
+        <v>1.6479</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3397</v>
+        <v>1.3959</v>
       </c>
       <c r="G4" t="n">
         <v>2.6557</v>
@@ -766,13 +766,13 @@
         <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9978</v>
+        <v>-0.3699</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1855</v>
+        <v>-0.6138</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1877</v>
+        <v>0.2439</v>
       </c>
       <c r="V4" t="n">
         <v>2.3438</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1107</v>
+        <v>2.3836</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1107</v>
+        <v>-0.8316</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3.2152</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1107</v>
+        <v>1.7317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3027</v>
+        <v>1.001</v>
       </c>
       <c r="I5" t="n">
-        <v>1.808</v>
+        <v>0.7307</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1107</v>
+        <v>1.4872</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3027</v>
+        <v>1.447</v>
       </c>
       <c r="L5" t="n">
-        <v>1.808</v>
+        <v>0.0402</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.2446</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.446</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.6905</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.9733</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.2689</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.3397</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0299</v>
+        <v>2.1107</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7921</v>
+        <v>2.1107</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8221</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7317</v>
+        <v>2.1107</v>
       </c>
       <c r="H6" t="n">
-        <v>1.001</v>
+        <v>0.3027</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7307</v>
+        <v>1.808</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4872</v>
+        <v>2.1107</v>
       </c>
       <c r="K6" t="n">
-        <v>1.447</v>
+        <v>0.3027</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0402</v>
+        <v>1.808</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2446</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.446</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6905</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9733</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6225000000000001</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1103</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7328</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5051</v>
+        <v>1.3928</v>
       </c>
       <c r="E7" t="n">
         <v>0.5411</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9641</v>
+        <v>0.8517</v>
       </c>
       <c r="G7" t="n">
         <v>0.8716</v>
@@ -1000,13 +1000,13 @@
         <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0389</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1248</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1637</v>
+        <v>0.0514</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>J. CEBRIAN ROSAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0144</v>
+        <v>0.2179</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2626</v>
+        <v>0.6495</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2482</v>
+        <v>-0.4316</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8021</v>
+        <v>1.0832</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4138</v>
+        <v>0.9951</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3883</v>
+        <v>0.0881</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3105</v>
+        <v>1.2404</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0694</v>
+        <v>1.3052</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2411</v>
+        <v>-0.0648</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5084</v>
+        <v>-0.1572</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6556</v>
+        <v>-0.3101</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1472</v>
+        <v>0.1529</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5858</v>
+        <v>1.5858</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3964</v>
+        <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6988</v>
+        <v>-0.9774</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1944</v>
+        <v>-0.5909</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8933</v>
+        <v>-0.3865</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0704</v>
+        <v>-1.4737</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5331</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2811</v>
+        <v>-0.1407</v>
       </c>
       <c r="E10" t="n">
         <v>-0.5629999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2819</v>
+        <v>0.4223</v>
       </c>
       <c r="G10" t="n">
         <v>0.8146</v>
@@ -1234,13 +1234,13 @@
         <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5011</v>
+        <v>-0.3607</v>
       </c>
       <c r="T10" t="n">
         <v>-0.4992</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0019</v>
+        <v>0.1385</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CEBRIAN ROSAS</t>
+          <t>A. BUZZO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4423</v>
+        <v>-0.6344</v>
       </c>
       <c r="E11" t="n">
-        <v>0.242</v>
+        <v>-3.5737</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6843</v>
+        <v>2.9393</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0832</v>
+        <v>-1.727</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9951</v>
+        <v>1.2441</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0881</v>
+        <v>-2.9711</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2404</v>
+        <v>-1.4379</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3052</v>
+        <v>1.9578</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0648</v>
+        <v>-3.3957</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1572</v>
+        <v>-0.2891</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3101</v>
+        <v>-0.7137</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1529</v>
+        <v>0.4246</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5858</v>
+        <v>3.1716</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6376</v>
+        <v>-0.2423</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9984</v>
+        <v>-0.4954</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6392</v>
+        <v>0.253</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4737</v>
+        <v>1.1367</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.3329</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4737</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BUZZO</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9502</v>
+        <v>-0.7693</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4511</v>
+        <v>-0.5682</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5009</v>
+        <v>-0.201</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.727</v>
+        <v>0.8021</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2441</v>
+        <v>0.4138</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9711</v>
+        <v>0.3883</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4379</v>
+        <v>1.3105</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9578</v>
+        <v>1.0694</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.3957</v>
+        <v>0.2411</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2891</v>
+        <v>-0.5084</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7137</v>
+        <v>-0.6556</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4246</v>
+        <v>0.1472</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1716</v>
+        <v>0.3964</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5581</v>
+        <v>-0.056</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3727</v>
+        <v>-0.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8146</v>
+        <v>0.444</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1367</v>
+        <v>0.0704</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3329</v>
+        <v>0.6036</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1962</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.5728</v>
+        <v>-1.8272</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1013</v>
+        <v>-1.5699</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5285</v>
+        <v>-0.2573</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6964</v>
+        <v>-0.0824</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0217</v>
+        <v>-0.8017</v>
       </c>
       <c r="I13" t="n">
-        <v>1.718</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5392</v>
+        <v>-0.5715</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3701</v>
+        <v>-0.6117</v>
       </c>
       <c r="L13" t="n">
-        <v>1.169</v>
+        <v>0.0402</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1572</v>
+        <v>0.4891</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3918</v>
+        <v>-0.19</v>
       </c>
       <c r="O13" t="n">
-        <v>0.549</v>
+        <v>0.6791</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9733</v>
+        <v>0.1982</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0521</v>
+        <v>-0.2028</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6719000000000001</v>
+        <v>-0.0072</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3802</v>
+        <v>-0.1956</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3479</v>
+        <v>-1.7403</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.3479</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.1423</v>
+        <v>-2.1945</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6323</v>
+        <v>-3.6107</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.51</v>
+        <v>1.4162</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0824</v>
+        <v>1.6964</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8017</v>
+        <v>-0.0217</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7193000000000001</v>
+        <v>1.718</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5715</v>
+        <v>1.5392</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6117</v>
+        <v>0.3701</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0402</v>
+        <v>1.169</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4891</v>
+        <v>0.1572</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.19</v>
+        <v>-0.3918</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6791</v>
+        <v>0.549</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1982</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5179</v>
+        <v>0.4304</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0696</v>
+        <v>0.1625</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4483</v>
+        <v>0.2679</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7403</v>
+        <v>-1.3479</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.3479</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.4077</v>
+        <v>11.7197</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4966</v>
+        <v>-1.1847</v>
       </c>
       <c r="F15" t="n">
         <v>12.9045</v>
@@ -1606,7 +1606,7 @@
         <v>4.5829</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6596000000000001</v>
+        <v>0.6596</v>
       </c>
       <c r="N15" t="n">
         <v>-2.1709</v>
@@ -1624,10 +1624,10 @@
         <v>16.8488</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1477</v>
+        <v>-1.8356</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.6234</v>
+        <v>-2.3115</v>
       </c>
       <c r="U15" t="n">
         <v>0.4758000000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7137</v>
+        <v>6.5319</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7201</v>
+        <v>4.2294</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9936</v>
+        <v>2.3025</v>
       </c>
       <c r="G16" t="n">
         <v>5.7392</v>
@@ -1702,13 +1702,13 @@
         <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9503</v>
+        <v>-0.1321</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6753</v>
+        <v>-0.166</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.275</v>
+        <v>0.0339</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4627</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1291</v>
+        <v>0.5802</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9773</v>
+        <v>0.653</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1518</v>
+        <v>-0.0728</v>
       </c>
       <c r="G17" t="n">
         <v>-2.6843</v>
@@ -1780,13 +1780,13 @@
         <v>3.1716</v>
       </c>
       <c r="S17" t="n">
-        <v>2.754</v>
+        <v>1.205</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7844</v>
+        <v>0.46</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9696</v>
+        <v>0.745</v>
       </c>
       <c r="V17" t="n">
         <v>0.8701</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>P. MONTES EGEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-1.0327</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8471</v>
+        <v>-1.823</v>
       </c>
       <c r="F18" t="n">
-        <v>2.151</v>
+        <v>0.7904</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5273</v>
+        <v>0.7234</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8357</v>
+        <v>0.1801</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.363</v>
+        <v>0.5433</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.0404</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2984</v>
+        <v>0.0404</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.5045</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3212</v>
+        <v>0.6831</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4627</v>
+        <v>0.1398</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1415</v>
+        <v>0.5433</v>
       </c>
       <c r="P18" t="n">
+        <v>-1.784</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.9822</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-4.9556</v>
-      </c>
       <c r="R18" t="n">
-        <v>2.9733</v>
+        <v>0.1982</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8838</v>
+        <v>-0.2386</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8518</v>
+        <v>-0.1477</v>
       </c>
       <c r="U18" t="n">
-        <v>1.032</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0704</v>
+        <v>0.2666</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4627</v>
+        <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MONTES EGEA</t>
+          <t>J. RAMIREZ GUERRA-LIBRERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9941</v>
+        <v>-1.173</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9249</v>
+        <v>1.6187</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9307</v>
+        <v>-2.7917</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7234</v>
+        <v>-2.8592</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1801</v>
+        <v>-1.629</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5433</v>
+        <v>-1.2302</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0404</v>
+        <v>0.3407</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0404</v>
+        <v>0.377</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.0363</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6831</v>
+        <v>-3.1999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1398</v>
+        <v>-2.006</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5433</v>
+        <v>-1.1939</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1982</v>
+        <v>2.1805</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2001</v>
+        <v>0.1093</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2496</v>
+        <v>0.0708</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0495</v>
+        <v>0.0384</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2666</v>
+        <v>-0.6036</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RAMIREZ GUERRA-LIBRERO</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4642</v>
+        <v>-1.8127</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7206</v>
+        <v>-3.4583</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1848</v>
+        <v>1.6456</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8592</v>
+        <v>-0.5273</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.629</v>
+        <v>2.8357</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2302</v>
+        <v>-3.363</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3407</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.377</v>
+        <v>4.2984</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0363</v>
+        <v>-3.5045</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1999</v>
+        <v>-1.3212</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.006</v>
+        <v>-1.4627</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1939</v>
+        <v>0.1415</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1805</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.9556</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1805</v>
+        <v>2.9733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.182</v>
+        <v>0.7672</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1727</v>
+        <v>0.2406</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3547</v>
+        <v>0.5266</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6036</v>
+        <v>-0.0704</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2071</v>
+        <v>0.4627</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8107</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1886</v>
+        <v>-2.2272</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.7594</v>
+        <v>-3.6575</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5708</v>
+        <v>1.4304</v>
       </c>
       <c r="G21" t="n">
         <v>-6.3204</v>
@@ -2092,13 +2092,13 @@
         <v>3.3698</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5966</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1906</v>
+        <v>-0.0888</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7872</v>
+        <v>0.6468</v>
       </c>
       <c r="V21" t="n">
         <v>2.1476</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1033</v>
+        <v>-3.4359</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.529</v>
+        <v>-3.9178</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4257</v>
+        <v>0.4819</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2735</v>
@@ -2170,13 +2170,13 @@
         <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4948</v>
+        <v>0.1725</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0608</v>
+        <v>-0.4495</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5659</v>
+        <v>0.6221</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5331</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4581</v>
+        <v>-4.3177</v>
       </c>
       <c r="E23" t="n">
         <v>-2.8262</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6319</v>
+        <v>-1.4915</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8424</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2808</v>
+        <v>-0.1404</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2458</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.035</v>
+        <v>0.1054</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7403</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.346</v>
+        <v>-4.5206</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.4356</v>
+        <v>-3.7225</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9103</v>
+        <v>-0.798</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1602</v>
@@ -2326,13 +2326,13 @@
         <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9786</v>
+        <v>-0.1532</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8625</v>
+        <v>-0.1494</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1161</v>
+        <v>-0.0038</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.4076</v>
+        <v>-11.4077</v>
       </c>
       <c r="E25" t="n">
         <v>-12.9042</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4966</v>
+        <v>1.4968</v>
       </c>
       <c r="G25" t="n">
         <v>-14.2047</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.791099999999999</v>
+        <v>-6.7911</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.413599999999999</v>
+        <v>-7.4136</v>
       </c>
       <c r="J25" t="n">
         <v>-0.6595000000000004</v>
@@ -2389,7 +2389,7 @@
         <v>-13.5451</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.962200000000001</v>
+        <v>-8.962199999999999</v>
       </c>
       <c r="O25" t="n">
         <v>-4.5829</v>
@@ -2404,13 +2404,13 @@
         <v>18.8313</v>
       </c>
       <c r="S25" t="n">
-        <v>2.1478</v>
+        <v>2.1477</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4757</v>
+        <v>-0.4758</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6234</v>
+        <v>2.6235</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3329</v>
